--- a/bronbestanden/eerstejaarsquiz_template.xlsx
+++ b/bronbestanden/eerstejaarsquiz_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Thomas/Dropbox/1_Projects_ongoing/lingquiztics/quiz_europese_taalkunde_2026/bronbestanden/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07F5DAC-4A5A-1443-B8D7-651C0DB32DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC8BE48-44F2-244C-BF46-4B554FCF8FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
